--- a/src/attributions/attributions_saliency_traj_128.xlsx
+++ b/src/attributions/attributions_saliency_traj_128.xlsx
@@ -1568,1709 +1568,1709 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>0.518732488155365</v>
+        <v>0.001526632579043508</v>
       </c>
       <c r="B3" t="n">
-        <v>0.5316336750984192</v>
+        <v>0.003692843485623598</v>
       </c>
       <c r="C3" t="n">
-        <v>0.6289333701133728</v>
+        <v>0.001564541598781943</v>
       </c>
       <c r="D3" t="n">
-        <v>0.25147345662117</v>
+        <v>0.0136514101177454</v>
       </c>
       <c r="E3" t="n">
-        <v>1.008325815200806</v>
+        <v>0.01037849299609661</v>
       </c>
       <c r="F3" t="n">
-        <v>0.2781845033168793</v>
+        <v>0.0116761177778244</v>
       </c>
       <c r="G3" t="n">
-        <v>0.001474291086196899</v>
+        <v>0.0007617291994392872</v>
       </c>
       <c r="H3" t="n">
-        <v>0.01697372645139694</v>
+        <v>0.01475858595222235</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1856520026922226</v>
+        <v>0.002799982437863946</v>
       </c>
       <c r="J3" t="n">
-        <v>0.1729345917701721</v>
+        <v>0.0004293328383937478</v>
       </c>
       <c r="K3" t="n">
-        <v>0.3482444584369659</v>
+        <v>0.01184950023889542</v>
       </c>
       <c r="L3" t="n">
-        <v>0.3479534387588501</v>
+        <v>0.005610442720353603</v>
       </c>
       <c r="M3" t="n">
-        <v>0.1156753897666931</v>
+        <v>0.01131847128272057</v>
       </c>
       <c r="N3" t="n">
-        <v>0.8882746696472168</v>
+        <v>0.00803507212549448</v>
       </c>
       <c r="O3" t="n">
-        <v>0.002514648716896772</v>
+        <v>0.0112547567114234</v>
       </c>
       <c r="P3" t="n">
-        <v>0.07121498882770538</v>
+        <v>0.009374609217047691</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.02641119621694088</v>
+        <v>0.0129964891821146</v>
       </c>
       <c r="R3" t="n">
-        <v>0.337518721818924</v>
+        <v>0.002513341140002012</v>
       </c>
       <c r="S3" t="n">
-        <v>0.02367529273033142</v>
+        <v>0.001885468489490449</v>
       </c>
       <c r="T3" t="n">
-        <v>0.2085833102464676</v>
+        <v>0.002566071460023522</v>
       </c>
       <c r="U3" t="n">
-        <v>0.218674510717392</v>
+        <v>0.0005894749192520976</v>
       </c>
       <c r="V3" t="n">
-        <v>0.108062669634819</v>
+        <v>0.0007764778565615416</v>
       </c>
       <c r="W3" t="n">
-        <v>0.1342399567365646</v>
+        <v>0.003590127686038613</v>
       </c>
       <c r="X3" t="n">
-        <v>0.1140609607100487</v>
+        <v>0.002453412627801299</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.06117454171180725</v>
+        <v>0.00115711847320199</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.1371892541646957</v>
+        <v>0.003985493909567595</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.06047366932034492</v>
+        <v>0.004739196971058846</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.1611845940351486</v>
+        <v>0.00546463206410408</v>
       </c>
       <c r="AC3" t="n">
-        <v>0.05409006774425507</v>
+        <v>0.006130655761808157</v>
       </c>
       <c r="AD3" t="n">
-        <v>0.04286545142531395</v>
+        <v>0.005309707019478083</v>
       </c>
       <c r="AE3" t="n">
-        <v>0.3025596737861633</v>
+        <v>0.0001661392161622643</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.06871569156646729</v>
+        <v>0.001607782673090696</v>
       </c>
       <c r="AG3" t="n">
-        <v>0.05785724520683289</v>
+        <v>0.002948187524452806</v>
       </c>
       <c r="AH3" t="n">
-        <v>0.01783028617501259</v>
+        <v>0.003927921876311302</v>
       </c>
       <c r="AI3" t="n">
-        <v>0.07965368032455444</v>
+        <v>0.01289735175669193</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0.1525722444057465</v>
+        <v>0.005848536267876625</v>
       </c>
       <c r="AK3" t="n">
-        <v>0.02068084478378296</v>
+        <v>0.005193211138248444</v>
       </c>
       <c r="AL3" t="n">
-        <v>0.2878142595291138</v>
+        <v>0.007157349959015846</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.1532977968454361</v>
+        <v>0.003659861627966166</v>
       </c>
       <c r="AN3" t="n">
-        <v>0.09217466413974762</v>
+        <v>0.005482113920152187</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.09447993338108063</v>
+        <v>0.006097359582781792</v>
       </c>
       <c r="AP3" t="n">
-        <v>0.0387738049030304</v>
+        <v>0.003023779485374689</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0.04698749631643295</v>
+        <v>0.002513845916837454</v>
       </c>
       <c r="AR3" t="n">
-        <v>0.01625905558466911</v>
+        <v>0.0004685972817242146</v>
       </c>
       <c r="AS3" t="n">
-        <v>0.124241515994072</v>
+        <v>0.001446875045076013</v>
       </c>
       <c r="AT3" t="n">
-        <v>0.2594515979290009</v>
+        <v>0.01006535068154335</v>
       </c>
       <c r="AU3" t="n">
-        <v>0.02631910890340805</v>
+        <v>0.01316962391138077</v>
       </c>
       <c r="AV3" t="n">
-        <v>0.4809629321098328</v>
+        <v>0.006107975728809834</v>
       </c>
       <c r="AW3" t="n">
-        <v>0.05221649259328842</v>
+        <v>0.005749429110437632</v>
       </c>
       <c r="AX3" t="n">
-        <v>0.8634307384490967</v>
+        <v>0.006542685907334089</v>
       </c>
       <c r="AY3" t="n">
-        <v>0.1585285663604736</v>
+        <v>0.003713997546583414</v>
       </c>
       <c r="AZ3" t="n">
-        <v>0.05920599773526192</v>
+        <v>0.00589762581512332</v>
       </c>
       <c r="BA3" t="n">
-        <v>0.2144436240196228</v>
+        <v>0.008965920656919479</v>
       </c>
       <c r="BB3" t="n">
-        <v>0.08401647955179214</v>
+        <v>0.001345918513834476</v>
       </c>
       <c r="BC3" t="n">
-        <v>0.3281638920307159</v>
+        <v>0.004605522379279137</v>
       </c>
       <c r="BD3" t="n">
-        <v>0.224338561296463</v>
+        <v>0.003982366528362036</v>
       </c>
       <c r="BE3" t="n">
-        <v>0.1490432024002075</v>
+        <v>0.001328551908954978</v>
       </c>
       <c r="BF3" t="n">
-        <v>0.1804174780845642</v>
+        <v>0.001882895594462752</v>
       </c>
       <c r="BG3" t="n">
-        <v>0.5574800372123718</v>
+        <v>0.01524604577571154</v>
       </c>
       <c r="BH3" t="n">
-        <v>0.5032857656478882</v>
+        <v>0.005207972601056099</v>
       </c>
       <c r="BI3" t="n">
-        <v>0.1090143546462059</v>
+        <v>0.001592741231434047</v>
       </c>
       <c r="BJ3" t="n">
-        <v>0.3206922113895416</v>
+        <v>0.004822524730116129</v>
       </c>
       <c r="BK3" t="n">
-        <v>0.4189245104789734</v>
+        <v>0.004249943420290947</v>
       </c>
       <c r="BL3" t="n">
-        <v>0.2692915201187134</v>
+        <v>0.001604102086275816</v>
       </c>
       <c r="BM3" t="n">
-        <v>0.1468667089939117</v>
+        <v>0.005150250624865294</v>
       </c>
       <c r="BN3" t="n">
-        <v>0.2028206139802933</v>
+        <v>0.001595693174749613</v>
       </c>
       <c r="BO3" t="n">
-        <v>0.2039062976837158</v>
+        <v>0.004599937237799168</v>
       </c>
       <c r="BP3" t="n">
-        <v>0.3488410413265228</v>
+        <v>0.007709486875683069</v>
       </c>
       <c r="BQ3" t="n">
-        <v>0.03394117951393127</v>
+        <v>0.000189333688467741</v>
       </c>
       <c r="BR3" t="n">
-        <v>0.1838487982749939</v>
+        <v>0.0006826376775279641</v>
       </c>
       <c r="BS3" t="n">
-        <v>0.07352456450462341</v>
+        <v>0.00908338651061058</v>
       </c>
       <c r="BT3" t="n">
-        <v>0.1130775362253189</v>
+        <v>0.002883570268750191</v>
       </c>
       <c r="BU3" t="n">
-        <v>0.104955293238163</v>
+        <v>0.003506187815219164</v>
       </c>
       <c r="BV3" t="n">
-        <v>0.07159591466188431</v>
+        <v>0.007778492290526628</v>
       </c>
       <c r="BW3" t="n">
-        <v>0.1662525236606598</v>
+        <v>0.002980404533445835</v>
       </c>
       <c r="BX3" t="n">
-        <v>0.1306954622268677</v>
+        <v>0.0009208142873831093</v>
       </c>
       <c r="BY3" t="n">
-        <v>0.5254098773002625</v>
+        <v>0.004763620905578136</v>
       </c>
       <c r="BZ3" t="n">
-        <v>0.06664920598268509</v>
+        <v>0.002386143431067467</v>
       </c>
       <c r="CA3" t="n">
-        <v>0.06401605904102325</v>
+        <v>0.001242243684828281</v>
       </c>
       <c r="CB3" t="n">
-        <v>0.1758464425802231</v>
+        <v>0.004514226224273443</v>
       </c>
       <c r="CC3" t="n">
-        <v>0.2596655189990997</v>
+        <v>0.008442235179245472</v>
       </c>
       <c r="CD3" t="n">
-        <v>0.05339837819337845</v>
+        <v>0.0004000038898084313</v>
       </c>
       <c r="CE3" t="n">
-        <v>0.1347250640392303</v>
+        <v>0.0001115223858505487</v>
       </c>
       <c r="CF3" t="n">
-        <v>0.13913594186306</v>
+        <v>0.0009544609347358346</v>
       </c>
       <c r="CG3" t="n">
-        <v>0.1095369756221771</v>
+        <v>0.0001330668455921113</v>
       </c>
       <c r="CH3" t="n">
-        <v>0.1906037926673889</v>
+        <v>0.0007100147195160389</v>
       </c>
       <c r="CI3" t="n">
-        <v>0.001319528091698885</v>
+        <v>0.002759522292762995</v>
       </c>
       <c r="CJ3" t="n">
-        <v>0.007941132411360741</v>
+        <v>0.002084779320284724</v>
       </c>
       <c r="CK3" t="n">
-        <v>0.01396334916353226</v>
+        <v>0.002419761149212718</v>
       </c>
       <c r="CL3" t="n">
-        <v>0.0108463242650032</v>
+        <v>0.001732093631289899</v>
       </c>
       <c r="CM3" t="n">
-        <v>0.005275476723909378</v>
+        <v>0.001495725940912962</v>
       </c>
       <c r="CN3" t="n">
-        <v>0.1884082853794098</v>
+        <v>0.006363928783684969</v>
       </c>
       <c r="CO3" t="n">
-        <v>0.1629605293273926</v>
+        <v>0.005020844284445047</v>
       </c>
       <c r="CP3" t="n">
-        <v>0.280005156993866</v>
+        <v>0.01127423718571663</v>
       </c>
       <c r="CQ3" t="n">
-        <v>0.590599536895752</v>
+        <v>0.006156299263238907</v>
       </c>
       <c r="CR3" t="n">
-        <v>0.08972786366939545</v>
+        <v>0.003599324729293585</v>
       </c>
       <c r="CS3" t="n">
-        <v>0.1920211315155029</v>
+        <v>0.004912968259304762</v>
       </c>
       <c r="CT3" t="n">
-        <v>0.04865116998553276</v>
+        <v>0.01094970479607582</v>
       </c>
       <c r="CU3" t="n">
-        <v>0.04621680825948715</v>
+        <v>0.0002858366933651268</v>
       </c>
       <c r="CV3" t="n">
-        <v>0.007084798067808151</v>
+        <v>0.0006891656084917486</v>
       </c>
       <c r="CW3" t="n">
-        <v>0.1411769241094589</v>
+        <v>0.001466625137254596</v>
       </c>
       <c r="CX3" t="n">
-        <v>0.09811133146286011</v>
+        <v>0.0003846878244075924</v>
       </c>
       <c r="CY3" t="n">
-        <v>0.1333299577236176</v>
+        <v>5.789962597191334e-05</v>
       </c>
       <c r="CZ3" t="n">
-        <v>0.09578926861286163</v>
+        <v>1.126830466091633e-05</v>
       </c>
       <c r="DA3" t="n">
-        <v>0.02139968425035477</v>
+        <v>0.003337159985676408</v>
       </c>
       <c r="DB3" t="n">
-        <v>0.0009715892374515533</v>
+        <v>0.001696705119684339</v>
       </c>
       <c r="DC3" t="n">
-        <v>0.005416764877736568</v>
+        <v>0.00246416823938489</v>
       </c>
       <c r="DD3" t="n">
-        <v>0.018059017136693</v>
+        <v>0.001853586174547672</v>
       </c>
       <c r="DE3" t="n">
-        <v>0.2452234625816345</v>
+        <v>0.003428187686949968</v>
       </c>
       <c r="DF3" t="n">
-        <v>0.1230483055114746</v>
+        <v>0.001994282007217407</v>
       </c>
       <c r="DG3" t="n">
-        <v>0.1923292279243469</v>
+        <v>0.0009222914231941104</v>
       </c>
       <c r="DH3" t="n">
-        <v>0.6173896789550781</v>
+        <v>0.001775029697455466</v>
       </c>
       <c r="DI3" t="n">
-        <v>0.2074626237154007</v>
+        <v>0.009162751957774162</v>
       </c>
       <c r="DJ3" t="n">
-        <v>0.1535195857286453</v>
+        <v>0.006311479955911636</v>
       </c>
       <c r="DK3" t="n">
-        <v>0.04120104387402534</v>
+        <v>0.002513048471882939</v>
       </c>
       <c r="DL3" t="n">
-        <v>0.009553556330502033</v>
+        <v>0.006139533128589392</v>
       </c>
       <c r="DM3" t="n">
-        <v>0.02381911501288414</v>
+        <v>0.008183312602341175</v>
       </c>
       <c r="DN3" t="n">
-        <v>0.1363124698400497</v>
+        <v>0.006859592627733946</v>
       </c>
       <c r="DO3" t="n">
-        <v>0.2234256863594055</v>
+        <v>0.0009827375179156661</v>
       </c>
       <c r="DP3" t="n">
-        <v>0.145975261926651</v>
+        <v>0.003348095109686255</v>
       </c>
       <c r="DQ3" t="n">
-        <v>0.1398289501667023</v>
+        <v>0.00220166239887476</v>
       </c>
       <c r="DR3" t="n">
-        <v>0.3163182139396667</v>
+        <v>0.006687754765152931</v>
       </c>
       <c r="DS3" t="n">
-        <v>0.1272043436765671</v>
+        <v>0.002211654558777809</v>
       </c>
       <c r="DT3" t="n">
-        <v>0.1571699380874634</v>
+        <v>0.00238425494171679</v>
       </c>
       <c r="DU3" t="n">
-        <v>0.1494054198265076</v>
+        <v>0.005499398801475763</v>
       </c>
       <c r="DV3" t="n">
-        <v>0.1872348934412003</v>
+        <v>0.002239330904558301</v>
       </c>
       <c r="DW3" t="n">
-        <v>0.02633764781057835</v>
+        <v>0.005643958691507578</v>
       </c>
       <c r="DX3" t="n">
-        <v>0.1149201244115829</v>
+        <v>0.002532639540731907</v>
       </c>
       <c r="DY3" t="n">
-        <v>0.1490999013185501</v>
+        <v>0.003770209616050124</v>
       </c>
       <c r="DZ3" t="n">
-        <v>0.2317953258752823</v>
+        <v>0.0002323458320461214</v>
       </c>
       <c r="EA3" t="n">
-        <v>0.111133836209774</v>
+        <v>0.01008548587560654</v>
       </c>
       <c r="EB3" t="n">
-        <v>0.03911703824996948</v>
+        <v>0.005446168128401041</v>
       </c>
       <c r="EC3" t="n">
-        <v>0.04945838451385498</v>
+        <v>0.0008430827874690294</v>
       </c>
       <c r="ED3" t="n">
-        <v>0.02498351410031319</v>
+        <v>0.007148790638893843</v>
       </c>
       <c r="EE3" t="n">
-        <v>0.1402898728847504</v>
+        <v>0.003521963022649288</v>
       </c>
       <c r="EF3" t="n">
-        <v>0.02592691406607628</v>
+        <v>0.003016738221049309</v>
       </c>
       <c r="EG3" t="n">
-        <v>0.06668712198734283</v>
+        <v>0.004020113032311201</v>
       </c>
       <c r="EH3" t="n">
-        <v>0.2579258978366852</v>
+        <v>0.0007830264512449503</v>
       </c>
       <c r="EI3" t="n">
-        <v>0.2218336462974548</v>
+        <v>0.002755924360826612</v>
       </c>
       <c r="EJ3" t="n">
-        <v>0.05060270801186562</v>
+        <v>0.004821576178073883</v>
       </c>
       <c r="EK3" t="n">
-        <v>0.1213567107915878</v>
+        <v>0.0006160931661725044</v>
       </c>
       <c r="EL3" t="n">
-        <v>0.001975096762180328</v>
+        <v>0.003322794567793608</v>
       </c>
       <c r="EM3" t="n">
-        <v>0.06954517960548401</v>
+        <v>0.003057897090911865</v>
       </c>
       <c r="EN3" t="n">
-        <v>0.05846498534083366</v>
+        <v>0.0006787704769521952</v>
       </c>
       <c r="EO3" t="n">
-        <v>0.1563653200864792</v>
+        <v>0.0007821418694220483</v>
       </c>
       <c r="EP3" t="n">
-        <v>0.03385762125253677</v>
+        <v>0.0009421868016943336</v>
       </c>
       <c r="EQ3" t="n">
-        <v>0.0187741257250309</v>
+        <v>4.764906043419614e-05</v>
       </c>
       <c r="ER3" t="n">
-        <v>0.2319753170013428</v>
+        <v>0.003319829935207963</v>
       </c>
       <c r="ES3" t="n">
-        <v>0.2924412190914154</v>
+        <v>0.0004137405194342136</v>
       </c>
       <c r="ET3" t="n">
-        <v>0.05435751751065254</v>
+        <v>0.002078135963529348</v>
       </c>
       <c r="EU3" t="n">
-        <v>0.04259458929300308</v>
+        <v>0.0003406712203286588</v>
       </c>
       <c r="EV3" t="n">
-        <v>0.02590357325971127</v>
+        <v>0.004295284394174814</v>
       </c>
       <c r="EW3" t="n">
-        <v>0.1630536317825317</v>
+        <v>0.007386184763163328</v>
       </c>
       <c r="EX3" t="n">
-        <v>0.01750178262591362</v>
+        <v>0.0003354063665028661</v>
       </c>
       <c r="EY3" t="n">
-        <v>0.07578318566083908</v>
+        <v>0.0009122961200773716</v>
       </c>
       <c r="EZ3" t="n">
-        <v>0.0933910608291626</v>
+        <v>0.00100877764634788</v>
       </c>
       <c r="FA3" t="n">
-        <v>0.07936812192201614</v>
+        <v>0.001466147252358496</v>
       </c>
       <c r="FB3" t="n">
-        <v>0.111648753285408</v>
+        <v>0.001488517038524151</v>
       </c>
       <c r="FC3" t="n">
-        <v>0.04364107921719551</v>
+        <v>0.002479178365319967</v>
       </c>
       <c r="FD3" t="n">
-        <v>0.05975193902850151</v>
+        <v>0.002223991323262453</v>
       </c>
       <c r="FE3" t="n">
-        <v>0.01927242614328861</v>
+        <v>0.004365494009107351</v>
       </c>
       <c r="FF3" t="n">
-        <v>0.008661303669214249</v>
+        <v>0.003452911972999573</v>
       </c>
       <c r="FG3" t="n">
-        <v>0.04217254742980003</v>
+        <v>0.005551488138735294</v>
       </c>
       <c r="FH3" t="n">
-        <v>0.0460895262658596</v>
+        <v>0.002289153635501862</v>
       </c>
       <c r="FI3" t="n">
-        <v>0.04846252873539925</v>
+        <v>0.002680973615497351</v>
       </c>
       <c r="FJ3" t="n">
-        <v>0.1307123899459839</v>
+        <v>0.002282646019011736</v>
       </c>
       <c r="FK3" t="n">
-        <v>0.1520342975854874</v>
+        <v>0.003523061517626047</v>
       </c>
       <c r="FL3" t="n">
-        <v>0.05047869682312012</v>
+        <v>0.001860793330706656</v>
       </c>
       <c r="FM3" t="n">
-        <v>0.197992354631424</v>
+        <v>0.004955499898642302</v>
       </c>
       <c r="FN3" t="n">
-        <v>0.005067359656095505</v>
+        <v>0.0007216639933176339</v>
       </c>
       <c r="FO3" t="n">
-        <v>0.1324134767055511</v>
+        <v>0.0006532252300530672</v>
       </c>
       <c r="FP3" t="n">
-        <v>0.1274519711732864</v>
+        <v>0.004560463130474091</v>
       </c>
       <c r="FQ3" t="n">
-        <v>0.1315889954566956</v>
+        <v>0.006372480187565088</v>
       </c>
       <c r="FR3" t="n">
-        <v>0.1585732996463776</v>
+        <v>0.004373321309685707</v>
       </c>
       <c r="FS3" t="n">
-        <v>0.1261947154998779</v>
+        <v>0.004753775428980589</v>
       </c>
       <c r="FT3" t="n">
-        <v>0.256826639175415</v>
+        <v>0.02268307469785213</v>
       </c>
       <c r="FU3" t="n">
-        <v>0.1723895370960236</v>
+        <v>0.007452198304235935</v>
       </c>
       <c r="FV3" t="n">
-        <v>0.05596822872757912</v>
+        <v>0.002836992964148521</v>
       </c>
       <c r="FW3" t="n">
-        <v>0.2947936058044434</v>
+        <v>0.003929344471544027</v>
       </c>
       <c r="FX3" t="n">
-        <v>0.05909900367259979</v>
+        <v>2.341525396332145e-05</v>
       </c>
       <c r="FY3" t="n">
-        <v>0.03142775222659111</v>
+        <v>0.0006868885830044746</v>
       </c>
       <c r="FZ3" t="n">
-        <v>0.2469455450773239</v>
+        <v>0.002989518688991666</v>
       </c>
       <c r="GA3" t="n">
-        <v>0.1077675521373749</v>
+        <v>0.002208651276305318</v>
       </c>
       <c r="GB3" t="n">
-        <v>0.1137115508317947</v>
+        <v>0.01368990261107683</v>
       </c>
       <c r="GC3" t="n">
-        <v>0.09333084523677826</v>
+        <v>0.003620501840487123</v>
       </c>
       <c r="GD3" t="n">
-        <v>0.1416878700256348</v>
+        <v>0.0007541496306657791</v>
       </c>
       <c r="GE3" t="n">
-        <v>0.1370646953582764</v>
+        <v>0.0003404211602173746</v>
       </c>
       <c r="GF3" t="n">
-        <v>0.06194289773702621</v>
+        <v>0.002286646515130997</v>
       </c>
       <c r="GG3" t="n">
-        <v>0.04642025381326675</v>
+        <v>0.002582465298473835</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>0.05197950080037117</v>
+        <v>0.06967649608850479</v>
       </c>
       <c r="B4" t="n">
-        <v>0.4855176508426666</v>
+        <v>0.4467262625694275</v>
       </c>
       <c r="C4" t="n">
-        <v>0.02821108140051365</v>
+        <v>0.1441876441240311</v>
       </c>
       <c r="D4" t="n">
-        <v>0.2809586524963379</v>
+        <v>0.8926724195480347</v>
       </c>
       <c r="E4" t="n">
-        <v>0.01214724406599998</v>
+        <v>0.03326022997498512</v>
       </c>
       <c r="F4" t="n">
-        <v>0.1198822185397148</v>
+        <v>0.1970879584550858</v>
       </c>
       <c r="G4" t="n">
-        <v>0.01669128611683846</v>
+        <v>0.2820659875869751</v>
       </c>
       <c r="H4" t="n">
-        <v>0.05028551816940308</v>
+        <v>0.3166835904121399</v>
       </c>
       <c r="I4" t="n">
-        <v>0.01909320428967476</v>
+        <v>0.02816789969801903</v>
       </c>
       <c r="J4" t="n">
-        <v>0.08649181574583054</v>
+        <v>0.03588388860225677</v>
       </c>
       <c r="K4" t="n">
-        <v>0.3276216983795166</v>
+        <v>0.3262712359428406</v>
       </c>
       <c r="L4" t="n">
-        <v>0.018982769921422</v>
+        <v>0.03142943978309631</v>
       </c>
       <c r="M4" t="n">
-        <v>0.2793785333633423</v>
+        <v>1.209661960601807</v>
       </c>
       <c r="N4" t="n">
-        <v>0.09670212119817734</v>
+        <v>0.01645399071276188</v>
       </c>
       <c r="O4" t="n">
-        <v>0.1668866276741028</v>
+        <v>0.246566042304039</v>
       </c>
       <c r="P4" t="n">
-        <v>0.01126629114151001</v>
+        <v>0.4070789217948914</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.02621287852525711</v>
+        <v>0.1226173639297485</v>
       </c>
       <c r="R4" t="n">
-        <v>0.05425384268164635</v>
+        <v>0.06424272805452347</v>
       </c>
       <c r="S4" t="n">
-        <v>0.01721889339387417</v>
+        <v>0.03485103696584702</v>
       </c>
       <c r="T4" t="n">
-        <v>0.06583236157894135</v>
+        <v>0.02382583729922771</v>
       </c>
       <c r="U4" t="n">
-        <v>0.01095103193074465</v>
+        <v>0.01809490658342838</v>
       </c>
       <c r="V4" t="n">
-        <v>0.06065648794174194</v>
+        <v>0.06794314086437225</v>
       </c>
       <c r="W4" t="n">
-        <v>0.02964404225349426</v>
+        <v>0.159177765250206</v>
       </c>
       <c r="X4" t="n">
-        <v>0.0288748387247324</v>
+        <v>0.1857160478830338</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.04264169931411743</v>
+        <v>0.0188752394169569</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.04172477871179581</v>
+        <v>0.1130287274718285</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.04102058336138725</v>
+        <v>0.07842759788036346</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.03264322876930237</v>
+        <v>0.01869340054690838</v>
       </c>
       <c r="AC4" t="n">
-        <v>0.06294571608304977</v>
+        <v>0.103749506175518</v>
       </c>
       <c r="AD4" t="n">
-        <v>0.005388098768889904</v>
+        <v>0.02651082724332809</v>
       </c>
       <c r="AE4" t="n">
-        <v>0.01555862277746201</v>
+        <v>0.009265415370464325</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.008819043636322021</v>
+        <v>0.06788256019353867</v>
       </c>
       <c r="AG4" t="n">
-        <v>0.005153689533472061</v>
+        <v>0.07886259257793427</v>
       </c>
       <c r="AH4" t="n">
-        <v>0.02922048605978489</v>
+        <v>0.04791157320141792</v>
       </c>
       <c r="AI4" t="n">
-        <v>0.01496904622763395</v>
+        <v>0.012320376932621</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0.02378188632428646</v>
+        <v>0.182134211063385</v>
       </c>
       <c r="AK4" t="n">
-        <v>0.02819530293345451</v>
+        <v>0.06482221931219101</v>
       </c>
       <c r="AL4" t="n">
-        <v>0.05557640641927719</v>
+        <v>0.1054739058017731</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.005171684548258781</v>
+        <v>0.1389351040124893</v>
       </c>
       <c r="AN4" t="n">
-        <v>0.02974363230168819</v>
+        <v>0.179763451218605</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.02007430605590343</v>
+        <v>0.02452832274138927</v>
       </c>
       <c r="AP4" t="n">
-        <v>0.06696841865777969</v>
+        <v>0.1360273510217667</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0.01641109585762024</v>
+        <v>0.1262635737657547</v>
       </c>
       <c r="AR4" t="n">
-        <v>0.03013666160404682</v>
+        <v>0.03257903084158897</v>
       </c>
       <c r="AS4" t="n">
-        <v>0.02917324006557465</v>
+        <v>0.01925789006054401</v>
       </c>
       <c r="AT4" t="n">
-        <v>0.04557377099990845</v>
+        <v>0.04826997593045235</v>
       </c>
       <c r="AU4" t="n">
-        <v>0.3511514663696289</v>
+        <v>0.1138622462749481</v>
       </c>
       <c r="AV4" t="n">
-        <v>0.0002959193661808968</v>
+        <v>0.04124530404806137</v>
       </c>
       <c r="AW4" t="n">
-        <v>0.04788226634263992</v>
+        <v>0.483950287103653</v>
       </c>
       <c r="AX4" t="n">
-        <v>0.0887247622013092</v>
+        <v>0.4870339334011078</v>
       </c>
       <c r="AY4" t="n">
-        <v>0.01336588244885206</v>
+        <v>0.1136096343398094</v>
       </c>
       <c r="AZ4" t="n">
-        <v>0.0143206212669611</v>
+        <v>0.0257377028465271</v>
       </c>
       <c r="BA4" t="n">
-        <v>0.02431102097034454</v>
+        <v>0.05809200555086136</v>
       </c>
       <c r="BB4" t="n">
-        <v>0.03603310883045197</v>
+        <v>0.114897608757019</v>
       </c>
       <c r="BC4" t="n">
-        <v>0.02671853639185429</v>
+        <v>0.1042036116123199</v>
       </c>
       <c r="BD4" t="n">
-        <v>0.06959628313779831</v>
+        <v>0.1673276722431183</v>
       </c>
       <c r="BE4" t="n">
-        <v>0.06468752771615982</v>
+        <v>0.001232236623764038</v>
       </c>
       <c r="BF4" t="n">
-        <v>0.0732743889093399</v>
+        <v>0.006811656057834625</v>
       </c>
       <c r="BG4" t="n">
-        <v>0.1349589079618454</v>
+        <v>0.3089374005794525</v>
       </c>
       <c r="BH4" t="n">
-        <v>0.07127615064382553</v>
+        <v>0.1420031040906906</v>
       </c>
       <c r="BI4" t="n">
-        <v>0.06243941932916641</v>
+        <v>0.03688352555036545</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0.04777223616838455</v>
+        <v>0.2184204906225204</v>
       </c>
       <c r="BK4" t="n">
-        <v>0.01825359836220741</v>
+        <v>0.1838219612836838</v>
       </c>
       <c r="BL4" t="n">
-        <v>0.065602146089077</v>
+        <v>0.008601771667599678</v>
       </c>
       <c r="BM4" t="n">
-        <v>0.06649273633956909</v>
+        <v>0.0008185254409909248</v>
       </c>
       <c r="BN4" t="n">
-        <v>0.02059587463736534</v>
+        <v>0.02469358779489994</v>
       </c>
       <c r="BO4" t="n">
-        <v>0.05013670027256012</v>
+        <v>0.06212444603443146</v>
       </c>
       <c r="BP4" t="n">
-        <v>0.03147546574473381</v>
+        <v>0.04021036997437477</v>
       </c>
       <c r="BQ4" t="n">
-        <v>0.02302549034357071</v>
+        <v>0.14981909096241</v>
       </c>
       <c r="BR4" t="n">
-        <v>0.01705588586628437</v>
+        <v>0.06376016885042191</v>
       </c>
       <c r="BS4" t="n">
-        <v>0.0022702906280756</v>
+        <v>0.06832096725702286</v>
       </c>
       <c r="BT4" t="n">
-        <v>0.02627801708877087</v>
+        <v>0.02604159340262413</v>
       </c>
       <c r="BU4" t="n">
-        <v>0.03403905034065247</v>
+        <v>0.004732768982648849</v>
       </c>
       <c r="BV4" t="n">
-        <v>0.1710293889045715</v>
+        <v>0.02049528807401657</v>
       </c>
       <c r="BW4" t="n">
-        <v>0.02346931211650372</v>
+        <v>0.07388440519571304</v>
       </c>
       <c r="BX4" t="n">
-        <v>0.0272484328597784</v>
+        <v>0.4049220681190491</v>
       </c>
       <c r="BY4" t="n">
-        <v>0.01575826294720173</v>
+        <v>0.1623556166887283</v>
       </c>
       <c r="BZ4" t="n">
-        <v>0.0602298341691494</v>
+        <v>0.1450991183519363</v>
       </c>
       <c r="CA4" t="n">
-        <v>0.008172136731445789</v>
+        <v>0.03662183880805969</v>
       </c>
       <c r="CB4" t="n">
-        <v>0.01053509954363108</v>
+        <v>0.0764978900551796</v>
       </c>
       <c r="CC4" t="n">
-        <v>0.04238754883408546</v>
+        <v>0.05020798742771149</v>
       </c>
       <c r="CD4" t="n">
-        <v>0.02965495921671391</v>
+        <v>0.0351661816239357</v>
       </c>
       <c r="CE4" t="n">
-        <v>0.07924612611532211</v>
+        <v>0.1177766621112823</v>
       </c>
       <c r="CF4" t="n">
-        <v>0.03124220855534077</v>
+        <v>0.0301628727465868</v>
       </c>
       <c r="CG4" t="n">
-        <v>0.02855437248945236</v>
+        <v>0.313191682100296</v>
       </c>
       <c r="CH4" t="n">
-        <v>0.02494167163968086</v>
+        <v>0.01314286887645721</v>
       </c>
       <c r="CI4" t="n">
-        <v>0.02120761759579182</v>
+        <v>0.01278974767774343</v>
       </c>
       <c r="CJ4" t="n">
-        <v>0.02233831025660038</v>
+        <v>0.04130315780639648</v>
       </c>
       <c r="CK4" t="n">
-        <v>0.008766308426856995</v>
+        <v>0.0684744194149971</v>
       </c>
       <c r="CL4" t="n">
-        <v>0.01464071311056614</v>
+        <v>0.002347424160689116</v>
       </c>
       <c r="CM4" t="n">
-        <v>0.04900170117616653</v>
+        <v>0.01419484615325928</v>
       </c>
       <c r="CN4" t="n">
-        <v>0.01999267563223839</v>
+        <v>0.06414438039064407</v>
       </c>
       <c r="CO4" t="n">
-        <v>0.03428234159946442</v>
+        <v>0.2616840898990631</v>
       </c>
       <c r="CP4" t="n">
-        <v>0.08697895705699921</v>
+        <v>0.4970238506793976</v>
       </c>
       <c r="CQ4" t="n">
-        <v>0.06583730131387711</v>
+        <v>0.003212473122403026</v>
       </c>
       <c r="CR4" t="n">
-        <v>0.04710642993450165</v>
+        <v>0.08910707384347916</v>
       </c>
       <c r="CS4" t="n">
-        <v>0.0383949875831604</v>
+        <v>0.02759251371026039</v>
       </c>
       <c r="CT4" t="n">
-        <v>0.07376513630151749</v>
+        <v>0.1567359864711761</v>
       </c>
       <c r="CU4" t="n">
-        <v>0.002628300804644823</v>
+        <v>0.08751314878463745</v>
       </c>
       <c r="CV4" t="n">
-        <v>0.0272995512932539</v>
+        <v>0.0242618415504694</v>
       </c>
       <c r="CW4" t="n">
-        <v>0.06667393445968628</v>
+        <v>0.1193761229515076</v>
       </c>
       <c r="CX4" t="n">
-        <v>0.02971046604216099</v>
+        <v>0.00688512297347188</v>
       </c>
       <c r="CY4" t="n">
-        <v>0.05148841440677643</v>
+        <v>0.3271681666374207</v>
       </c>
       <c r="CZ4" t="n">
-        <v>0.03244812414050102</v>
+        <v>0.009857851080596447</v>
       </c>
       <c r="DA4" t="n">
-        <v>0.03134956955909729</v>
+        <v>0.009065263904631138</v>
       </c>
       <c r="DB4" t="n">
-        <v>0.02412066794931889</v>
+        <v>0.06501297652721405</v>
       </c>
       <c r="DC4" t="n">
-        <v>0.01420357637107372</v>
+        <v>0.07637343555688858</v>
       </c>
       <c r="DD4" t="n">
-        <v>0.005267268978059292</v>
+        <v>0.008651597425341606</v>
       </c>
       <c r="DE4" t="n">
-        <v>0.02347438782453537</v>
+        <v>0.02183916792273521</v>
       </c>
       <c r="DF4" t="n">
-        <v>0.04206426441669464</v>
+        <v>0.01340865157544613</v>
       </c>
       <c r="DG4" t="n">
-        <v>0.00222699181176722</v>
+        <v>0.09338237345218658</v>
       </c>
       <c r="DH4" t="n">
-        <v>0.06304179131984711</v>
+        <v>0.2091723084449768</v>
       </c>
       <c r="DI4" t="n">
-        <v>0.03516829013824463</v>
+        <v>0.0165619570761919</v>
       </c>
       <c r="DJ4" t="n">
-        <v>0.01694917865097523</v>
+        <v>0.03740485012531281</v>
       </c>
       <c r="DK4" t="n">
-        <v>0.005285978317260742</v>
+        <v>0.01903678104281425</v>
       </c>
       <c r="DL4" t="n">
-        <v>0.0109620438888669</v>
+        <v>0.3490207493305206</v>
       </c>
       <c r="DM4" t="n">
-        <v>0.01644724793732166</v>
+        <v>0.2013404965400696</v>
       </c>
       <c r="DN4" t="n">
-        <v>0.0538036935031414</v>
+        <v>0.01329721510410309</v>
       </c>
       <c r="DO4" t="n">
-        <v>0.03174745664000511</v>
+        <v>0.07214799523353577</v>
       </c>
       <c r="DP4" t="n">
-        <v>0.0309627465903759</v>
+        <v>0.03130479902029037</v>
       </c>
       <c r="DQ4" t="n">
-        <v>0.01972798816859722</v>
+        <v>0.1345312297344208</v>
       </c>
       <c r="DR4" t="n">
-        <v>0.03272543475031853</v>
+        <v>0.01279934681952</v>
       </c>
       <c r="DS4" t="n">
-        <v>0.05081082880496979</v>
+        <v>0.007251790724694729</v>
       </c>
       <c r="DT4" t="n">
-        <v>0.01234668493270874</v>
+        <v>0.09591502696275711</v>
       </c>
       <c r="DU4" t="n">
-        <v>0.006716395728290081</v>
+        <v>0.1186186000704765</v>
       </c>
       <c r="DV4" t="n">
-        <v>0.02624006569385529</v>
+        <v>0.2558268904685974</v>
       </c>
       <c r="DW4" t="n">
-        <v>0.03272098675370216</v>
+        <v>0.04460924863815308</v>
       </c>
       <c r="DX4" t="n">
-        <v>0.004032781347632408</v>
+        <v>0.04386742040514946</v>
       </c>
       <c r="DY4" t="n">
-        <v>0.0677015483379364</v>
+        <v>0.1040447875857353</v>
       </c>
       <c r="DZ4" t="n">
-        <v>0.01091496553272009</v>
+        <v>0.2166658341884613</v>
       </c>
       <c r="EA4" t="n">
-        <v>0.05943558737635612</v>
+        <v>0.0654105469584465</v>
       </c>
       <c r="EB4" t="n">
-        <v>0.02303313091397285</v>
+        <v>0.109035462141037</v>
       </c>
       <c r="EC4" t="n">
-        <v>0.003342850366607308</v>
+        <v>0.02023698762059212</v>
       </c>
       <c r="ED4" t="n">
-        <v>0.01345774158835411</v>
+        <v>0.3740821778774261</v>
       </c>
       <c r="EE4" t="n">
-        <v>0.01861121319234371</v>
+        <v>0.1900876760482788</v>
       </c>
       <c r="EF4" t="n">
-        <v>0.008914344012737274</v>
+        <v>0.2007953226566315</v>
       </c>
       <c r="EG4" t="n">
-        <v>0.03727654367685318</v>
+        <v>0.0686199963092804</v>
       </c>
       <c r="EH4" t="n">
-        <v>0.004861777648329735</v>
+        <v>0.1087958067655563</v>
       </c>
       <c r="EI4" t="n">
-        <v>0.02465972304344177</v>
+        <v>0.2453399300575256</v>
       </c>
       <c r="EJ4" t="n">
-        <v>0.0009001221042126417</v>
+        <v>0.01309432834386826</v>
       </c>
       <c r="EK4" t="n">
-        <v>0.01866279542446136</v>
+        <v>0.01044366788119078</v>
       </c>
       <c r="EL4" t="n">
-        <v>0.02220542542636395</v>
+        <v>0.02540750615298748</v>
       </c>
       <c r="EM4" t="n">
-        <v>0.002603403758257627</v>
+        <v>0.06040783226490021</v>
       </c>
       <c r="EN4" t="n">
-        <v>0.001197793055325747</v>
+        <v>0.02498368360102177</v>
       </c>
       <c r="EO4" t="n">
-        <v>0.02807551249861717</v>
+        <v>0.08668499439954758</v>
       </c>
       <c r="EP4" t="n">
-        <v>0.05919355526566505</v>
+        <v>0.1667365431785583</v>
       </c>
       <c r="EQ4" t="n">
-        <v>0.001089862664230168</v>
+        <v>0.04484985396265984</v>
       </c>
       <c r="ER4" t="n">
-        <v>0.04886192083358765</v>
+        <v>0.2021782696247101</v>
       </c>
       <c r="ES4" t="n">
-        <v>0.04754649847745895</v>
+        <v>0.1431992053985596</v>
       </c>
       <c r="ET4" t="n">
-        <v>0.1203116923570633</v>
+        <v>0.128130629658699</v>
       </c>
       <c r="EU4" t="n">
-        <v>0.03578749671578407</v>
+        <v>0.1368748843669891</v>
       </c>
       <c r="EV4" t="n">
-        <v>0.02975077554583549</v>
+        <v>0.07870659232139587</v>
       </c>
       <c r="EW4" t="n">
-        <v>0.007486818358302116</v>
+        <v>0.1632962822914124</v>
       </c>
       <c r="EX4" t="n">
-        <v>0.01790042780339718</v>
+        <v>0.02496731653809547</v>
       </c>
       <c r="EY4" t="n">
-        <v>0.0643375962972641</v>
+        <v>0.1303324997425079</v>
       </c>
       <c r="EZ4" t="n">
-        <v>0.0127679044380784</v>
+        <v>0.0302397646009922</v>
       </c>
       <c r="FA4" t="n">
-        <v>0.04154352843761444</v>
+        <v>0.3687536120414734</v>
       </c>
       <c r="FB4" t="n">
-        <v>0.02813980542123318</v>
+        <v>0.008622444234788418</v>
       </c>
       <c r="FC4" t="n">
-        <v>0.03011521883308887</v>
+        <v>0.01141665503382683</v>
       </c>
       <c r="FD4" t="n">
-        <v>0.02912266924977303</v>
+        <v>0.06021354347467422</v>
       </c>
       <c r="FE4" t="n">
-        <v>0.01190689392387867</v>
+        <v>0.1202383488416672</v>
       </c>
       <c r="FF4" t="n">
-        <v>0.0175220463424921</v>
+        <v>0.002991680288687348</v>
       </c>
       <c r="FG4" t="n">
-        <v>0.01674945652484894</v>
+        <v>0.01336119323968887</v>
       </c>
       <c r="FH4" t="n">
-        <v>0.03377683460712433</v>
+        <v>0.07245984673500061</v>
       </c>
       <c r="FI4" t="n">
-        <v>0.01513462886214256</v>
+        <v>0.02655763924121857</v>
       </c>
       <c r="FJ4" t="n">
-        <v>0.04156716912984848</v>
+        <v>0.1302969455718994</v>
       </c>
       <c r="FK4" t="n">
-        <v>0.0248387698084116</v>
+        <v>0.1007501259446144</v>
       </c>
       <c r="FL4" t="n">
-        <v>0.01405899971723557</v>
+        <v>0.04043947905302048</v>
       </c>
       <c r="FM4" t="n">
-        <v>0.006590384989976883</v>
+        <v>0.06790259480476379</v>
       </c>
       <c r="FN4" t="n">
-        <v>0.01440253108739853</v>
+        <v>0.06439337134361267</v>
       </c>
       <c r="FO4" t="n">
-        <v>0.02935420721769333</v>
+        <v>0.04505113884806633</v>
       </c>
       <c r="FP4" t="n">
-        <v>0.01829812489449978</v>
+        <v>0.1212862432003021</v>
       </c>
       <c r="FQ4" t="n">
-        <v>0.01927214674651623</v>
+        <v>0.3307202160358429</v>
       </c>
       <c r="FR4" t="n">
-        <v>0.0003578895702958107</v>
+        <v>0.1957615613937378</v>
       </c>
       <c r="FS4" t="n">
-        <v>0.0415644645690918</v>
+        <v>0.4118925631046295</v>
       </c>
       <c r="FT4" t="n">
-        <v>0.08517244458198547</v>
+        <v>0.1069942116737366</v>
       </c>
       <c r="FU4" t="n">
-        <v>0.01796434074640274</v>
+        <v>0.1680480986833572</v>
       </c>
       <c r="FV4" t="n">
-        <v>0.02178524434566498</v>
+        <v>0.009563993662595749</v>
       </c>
       <c r="FW4" t="n">
-        <v>0.01359726395457983</v>
+        <v>0.1361878365278244</v>
       </c>
       <c r="FX4" t="n">
-        <v>0.02338017150759697</v>
+        <v>0.1679007560014725</v>
       </c>
       <c r="FY4" t="n">
-        <v>0.06476226449012756</v>
+        <v>0.04968713968992233</v>
       </c>
       <c r="FZ4" t="n">
-        <v>0.02953805960714817</v>
+        <v>0.05645947903394699</v>
       </c>
       <c r="GA4" t="n">
-        <v>0.02361995354294777</v>
+        <v>0.0428738184273243</v>
       </c>
       <c r="GB4" t="n">
-        <v>0.01875373907387257</v>
+        <v>0.2884637415409088</v>
       </c>
       <c r="GC4" t="n">
-        <v>0.03131196647882462</v>
+        <v>0.1777776479721069</v>
       </c>
       <c r="GD4" t="n">
-        <v>0.04064767807722092</v>
+        <v>0.01367672253400087</v>
       </c>
       <c r="GE4" t="n">
-        <v>0.1108182817697525</v>
+        <v>0.2408189624547958</v>
       </c>
       <c r="GF4" t="n">
-        <v>0.008570335805416107</v>
+        <v>0.08267131447792053</v>
       </c>
       <c r="GG4" t="n">
-        <v>0.01625575870275497</v>
+        <v>0.01254221890121698</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>0.00442784558981657</v>
+        <v>0.03452390804886818</v>
       </c>
       <c r="B5" t="n">
-        <v>0.02644891664385796</v>
+        <v>0.1879175752401352</v>
       </c>
       <c r="C5" t="n">
-        <v>0.004728595726191998</v>
+        <v>0.07056383788585663</v>
       </c>
       <c r="D5" t="n">
-        <v>0.01396144740283489</v>
+        <v>0.022597411647439</v>
       </c>
       <c r="E5" t="n">
-        <v>0.02227663062512875</v>
+        <v>0.1238238215446472</v>
       </c>
       <c r="F5" t="n">
-        <v>0.09530112147331238</v>
+        <v>0.254153847694397</v>
       </c>
       <c r="G5" t="n">
-        <v>0.02063008211553097</v>
+        <v>0.03291820362210274</v>
       </c>
       <c r="H5" t="n">
-        <v>0.03063107281923294</v>
+        <v>0.1435451358556747</v>
       </c>
       <c r="I5" t="n">
-        <v>0.02705815061926842</v>
+        <v>0.03986046835780144</v>
       </c>
       <c r="J5" t="n">
-        <v>0.009620007127523422</v>
+        <v>0.0154905878007412</v>
       </c>
       <c r="K5" t="n">
-        <v>0.001516471616923809</v>
+        <v>0.2155716270208359</v>
       </c>
       <c r="L5" t="n">
-        <v>0.02176045998930931</v>
+        <v>0.1253339797258377</v>
       </c>
       <c r="M5" t="n">
-        <v>0.01025712676346302</v>
+        <v>0.0289706364274025</v>
       </c>
       <c r="N5" t="n">
-        <v>0.004359748680144548</v>
+        <v>0.2185728847980499</v>
       </c>
       <c r="O5" t="n">
-        <v>0.08198286592960358</v>
+        <v>0.2432488948106766</v>
       </c>
       <c r="P5" t="n">
-        <v>0.01162580028176308</v>
+        <v>0.0340518094599247</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.04499657824635506</v>
+        <v>0.1414333581924438</v>
       </c>
       <c r="R5" t="n">
-        <v>0.01177291292697191</v>
+        <v>0.05313252657651901</v>
       </c>
       <c r="S5" t="n">
-        <v>0.004556036554276943</v>
+        <v>0.0173353273421526</v>
       </c>
       <c r="T5" t="n">
-        <v>0.004568557254970074</v>
+        <v>0.06227239966392517</v>
       </c>
       <c r="U5" t="n">
-        <v>0.008362414315342903</v>
+        <v>0.03347746282815933</v>
       </c>
       <c r="V5" t="n">
-        <v>0.00729731610044837</v>
+        <v>0.04315147921442986</v>
       </c>
       <c r="W5" t="n">
-        <v>0.02790413424372673</v>
+        <v>0.08581846207380295</v>
       </c>
       <c r="X5" t="n">
-        <v>0.0083769541233778</v>
+        <v>0.03969887271523476</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.005876834969967604</v>
+        <v>0.003259822726249695</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.007372975815087557</v>
+        <v>0.009115118533372879</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.005319893360137939</v>
+        <v>0.05398380756378174</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.005028113722801208</v>
+        <v>0.04025651514530182</v>
       </c>
       <c r="AC5" t="n">
-        <v>0.01512375846505165</v>
+        <v>0.0299557764083147</v>
       </c>
       <c r="AD5" t="n">
-        <v>0.02703345566987991</v>
+        <v>0.02027424611151218</v>
       </c>
       <c r="AE5" t="n">
-        <v>0.006376053206622601</v>
+        <v>0.02004827931523323</v>
       </c>
       <c r="AF5" t="n">
-        <v>0.003627964295446873</v>
+        <v>0.04063991829752922</v>
       </c>
       <c r="AG5" t="n">
-        <v>0.0009949852246791124</v>
+        <v>0.05553542822599411</v>
       </c>
       <c r="AH5" t="n">
-        <v>0.0224299468100071</v>
+        <v>0.01197485253214836</v>
       </c>
       <c r="AI5" t="n">
-        <v>0.004626291804015636</v>
+        <v>0.01295103318989277</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0.009268177673220634</v>
+        <v>0.0001017521135509014</v>
       </c>
       <c r="AK5" t="n">
-        <v>0.004896057303994894</v>
+        <v>0.002831747755408287</v>
       </c>
       <c r="AL5" t="n">
-        <v>0.004807756748050451</v>
+        <v>0.02284958586096764</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.0002115801908075809</v>
+        <v>0.03342543542385101</v>
       </c>
       <c r="AN5" t="n">
-        <v>0.007168718613684177</v>
+        <v>0.0259685255587101</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.0110802911221981</v>
+        <v>0.007639245130121708</v>
       </c>
       <c r="AP5" t="n">
-        <v>0.007523083128035069</v>
+        <v>0.02930343896150589</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0.005668319296091795</v>
+        <v>0.01261482387781143</v>
       </c>
       <c r="AR5" t="n">
-        <v>0.002744578290730715</v>
+        <v>0.001772118732333183</v>
       </c>
       <c r="AS5" t="n">
-        <v>0.002847996540367603</v>
+        <v>0.01429760083556175</v>
       </c>
       <c r="AT5" t="n">
-        <v>0.00952478963881731</v>
+        <v>0.0005977116525173187</v>
       </c>
       <c r="AU5" t="n">
-        <v>0.02367560006678104</v>
+        <v>0.2731926441192627</v>
       </c>
       <c r="AV5" t="n">
-        <v>0.004953600931912661</v>
+        <v>0.009024355560541153</v>
       </c>
       <c r="AW5" t="n">
-        <v>0.03304009512066841</v>
+        <v>0.00627045426517725</v>
       </c>
       <c r="AX5" t="n">
-        <v>0.04857243597507477</v>
+        <v>0.02673509158194065</v>
       </c>
       <c r="AY5" t="n">
-        <v>0.05150039494037628</v>
+        <v>0.09086013585329056</v>
       </c>
       <c r="AZ5" t="n">
-        <v>0.01171196158975363</v>
+        <v>0.001896210014820099</v>
       </c>
       <c r="BA5" t="n">
-        <v>0.008943893946707249</v>
+        <v>0.04775379225611687</v>
       </c>
       <c r="BB5" t="n">
-        <v>0.0162830762565136</v>
+        <v>0.01440840866416693</v>
       </c>
       <c r="BC5" t="n">
-        <v>0.003206566441804171</v>
+        <v>0.06000947207212448</v>
       </c>
       <c r="BD5" t="n">
-        <v>0.005304973106831312</v>
+        <v>0.0342799574136734</v>
       </c>
       <c r="BE5" t="n">
-        <v>0.01486502680927515</v>
+        <v>0.02520368620753288</v>
       </c>
       <c r="BF5" t="n">
-        <v>0.006102991290390491</v>
+        <v>0.03140711784362793</v>
       </c>
       <c r="BG5" t="n">
-        <v>8.900044485926628e-05</v>
+        <v>0.06755807995796204</v>
       </c>
       <c r="BH5" t="n">
-        <v>0.02680080756545067</v>
+        <v>0.07310871779918671</v>
       </c>
       <c r="BI5" t="n">
-        <v>0.004686045460402966</v>
+        <v>0.01606458611786366</v>
       </c>
       <c r="BJ5" t="n">
-        <v>0.01449379976838827</v>
+        <v>0.04391094297170639</v>
       </c>
       <c r="BK5" t="n">
-        <v>0.002742755692452192</v>
+        <v>0.04777286946773529</v>
       </c>
       <c r="BL5" t="n">
-        <v>0.007782167289406061</v>
+        <v>0.004708146676421165</v>
       </c>
       <c r="BM5" t="n">
-        <v>0.03044067695736885</v>
+        <v>0.03222892433404922</v>
       </c>
       <c r="BN5" t="n">
-        <v>0.005861920770257711</v>
+        <v>0.1097031757235527</v>
       </c>
       <c r="BO5" t="n">
-        <v>0.006336776074022055</v>
+        <v>0.01326387841254473</v>
       </c>
       <c r="BP5" t="n">
-        <v>0.005669808015227318</v>
+        <v>0.0586327351629734</v>
       </c>
       <c r="BQ5" t="n">
-        <v>0.006402874365448952</v>
+        <v>0.05260807648301125</v>
       </c>
       <c r="BR5" t="n">
-        <v>0.008209865540266037</v>
+        <v>0.03103737719357014</v>
       </c>
       <c r="BS5" t="n">
-        <v>0.01158679090440273</v>
+        <v>0.03378721699118614</v>
       </c>
       <c r="BT5" t="n">
-        <v>0.01206782832741737</v>
+        <v>0.03280052915215492</v>
       </c>
       <c r="BU5" t="n">
-        <v>0.005304465070366859</v>
+        <v>0.02732037007808685</v>
       </c>
       <c r="BV5" t="n">
-        <v>0.008312656544148922</v>
+        <v>0.1539180278778076</v>
       </c>
       <c r="BW5" t="n">
-        <v>0.008283593691885471</v>
+        <v>0.007987953722476959</v>
       </c>
       <c r="BX5" t="n">
-        <v>0.01402527838945389</v>
+        <v>0.05543713271617889</v>
       </c>
       <c r="BY5" t="n">
-        <v>0.02447643131017685</v>
+        <v>0.05773160606622696</v>
       </c>
       <c r="BZ5" t="n">
-        <v>0.034329853951931</v>
+        <v>0.06598466634750366</v>
       </c>
       <c r="CA5" t="n">
-        <v>0.003842257894575596</v>
+        <v>5.419738590717316e-05</v>
       </c>
       <c r="CB5" t="n">
-        <v>0.002424886450171471</v>
+        <v>0.0266018770635128</v>
       </c>
       <c r="CC5" t="n">
-        <v>0.006566840223968029</v>
+        <v>0.02005010098218918</v>
       </c>
       <c r="CD5" t="n">
-        <v>0.001574086956679821</v>
+        <v>0.01348698139190674</v>
       </c>
       <c r="CE5" t="n">
-        <v>0.0008475224603898823</v>
+        <v>0.04319639503955841</v>
       </c>
       <c r="CF5" t="n">
-        <v>0.005348652601242065</v>
+        <v>0.0450197234749794</v>
       </c>
       <c r="CG5" t="n">
-        <v>0.00180165481287986</v>
+        <v>0.002939915284514427</v>
       </c>
       <c r="CH5" t="n">
-        <v>0.007513921242207289</v>
+        <v>0.03357118368148804</v>
       </c>
       <c r="CI5" t="n">
-        <v>0.01917770318686962</v>
+        <v>0.05396848171949387</v>
       </c>
       <c r="CJ5" t="n">
-        <v>0.0004667495377361774</v>
+        <v>0.01614215597510338</v>
       </c>
       <c r="CK5" t="n">
-        <v>0.008793718181550503</v>
+        <v>0.004275035113096237</v>
       </c>
       <c r="CL5" t="n">
-        <v>0.0006110362010076642</v>
+        <v>0.009075536392629147</v>
       </c>
       <c r="CM5" t="n">
-        <v>0.007866762578487396</v>
+        <v>0.01313845813274384</v>
       </c>
       <c r="CN5" t="n">
-        <v>0.01247899048030376</v>
+        <v>0.07788053900003433</v>
       </c>
       <c r="CO5" t="n">
-        <v>0.003628325648605824</v>
+        <v>0.02889244258403778</v>
       </c>
       <c r="CP5" t="n">
-        <v>0.01395053416490555</v>
+        <v>0.03078040480613708</v>
       </c>
       <c r="CQ5" t="n">
-        <v>0.03174686059355736</v>
+        <v>0.03910716995596886</v>
       </c>
       <c r="CR5" t="n">
-        <v>0.01320891082286835</v>
+        <v>0.00126956682652235</v>
       </c>
       <c r="CS5" t="n">
-        <v>0.009324217215180397</v>
+        <v>0.003740945365279913</v>
       </c>
       <c r="CT5" t="n">
-        <v>0.002603796543553472</v>
+        <v>0.05615941807627678</v>
       </c>
       <c r="CU5" t="n">
-        <v>0.01000735629349947</v>
+        <v>0.03911656513810158</v>
       </c>
       <c r="CV5" t="n">
-        <v>0.001207002671435475</v>
+        <v>0.001080401241779327</v>
       </c>
       <c r="CW5" t="n">
-        <v>0.003355611814185977</v>
+        <v>0.03518610075116158</v>
       </c>
       <c r="CX5" t="n">
-        <v>0.005493904929608107</v>
+        <v>0.05025094747543335</v>
       </c>
       <c r="CY5" t="n">
-        <v>0.001147671369835734</v>
+        <v>0.0001183357089757919</v>
       </c>
       <c r="CZ5" t="n">
-        <v>0.006474018096923828</v>
+        <v>0.041835717856884</v>
       </c>
       <c r="DA5" t="n">
-        <v>0.01608084142208099</v>
+        <v>0.06598518788814545</v>
       </c>
       <c r="DB5" t="n">
-        <v>0.001329233404248953</v>
+        <v>0.01607709005475044</v>
       </c>
       <c r="DC5" t="n">
-        <v>0.009274665266275406</v>
+        <v>0.005635450128465891</v>
       </c>
       <c r="DD5" t="n">
-        <v>0.003957969136536121</v>
+        <v>0.01712883077561855</v>
       </c>
       <c r="DE5" t="n">
-        <v>0.005923688411712646</v>
+        <v>0.02950146421790123</v>
       </c>
       <c r="DF5" t="n">
-        <v>0.007158208172768354</v>
+        <v>0.1354428231716156</v>
       </c>
       <c r="DG5" t="n">
-        <v>0.003989102318882942</v>
+        <v>0.0337742455303669</v>
       </c>
       <c r="DH5" t="n">
-        <v>0.03175516426563263</v>
+        <v>0.006815221160650253</v>
       </c>
       <c r="DI5" t="n">
-        <v>0.01556725800037384</v>
+        <v>0.02650351636111736</v>
       </c>
       <c r="DJ5" t="n">
-        <v>0.01331712305545807</v>
+        <v>0.06129950657486916</v>
       </c>
       <c r="DK5" t="n">
-        <v>0.005389486439526081</v>
+        <v>0.03606388345360756</v>
       </c>
       <c r="DL5" t="n">
-        <v>0.0157739445567131</v>
+        <v>0.04797673597931862</v>
       </c>
       <c r="DM5" t="n">
-        <v>0.02654312551021576</v>
+        <v>0.04106130078434944</v>
       </c>
       <c r="DN5" t="n">
-        <v>0.006637669634073973</v>
+        <v>0.03155535459518433</v>
       </c>
       <c r="DO5" t="n">
-        <v>0.008779933676123619</v>
+        <v>0.05765587836503983</v>
       </c>
       <c r="DP5" t="n">
-        <v>0.008544948883354664</v>
+        <v>0.0003109164535999298</v>
       </c>
       <c r="DQ5" t="n">
-        <v>0.01357682328671217</v>
+        <v>0.007450367324054241</v>
       </c>
       <c r="DR5" t="n">
-        <v>0.01223178114742041</v>
+        <v>0.03220325708389282</v>
       </c>
       <c r="DS5" t="n">
-        <v>0.007557201664894819</v>
+        <v>0.01085882168263197</v>
       </c>
       <c r="DT5" t="n">
-        <v>0.01522280462086201</v>
+        <v>0.0141081977635622</v>
       </c>
       <c r="DU5" t="n">
-        <v>0.006865677889436483</v>
+        <v>0.0001544872066006064</v>
       </c>
       <c r="DV5" t="n">
-        <v>0.004922641906887293</v>
+        <v>0.04808585345745087</v>
       </c>
       <c r="DW5" t="n">
-        <v>0.004972739145159721</v>
+        <v>0.02320654317736626</v>
       </c>
       <c r="DX5" t="n">
-        <v>0.001651655649766326</v>
+        <v>0.03965407609939575</v>
       </c>
       <c r="DY5" t="n">
-        <v>0.007375096436589956</v>
+        <v>0.04367724061012268</v>
       </c>
       <c r="DZ5" t="n">
-        <v>0.006659340113401413</v>
+        <v>0.00396119337528944</v>
       </c>
       <c r="EA5" t="n">
-        <v>0.001559318974614143</v>
+        <v>0.0001699755957815796</v>
       </c>
       <c r="EB5" t="n">
-        <v>0.01407800335437059</v>
+        <v>0.05064189806580544</v>
       </c>
       <c r="EC5" t="n">
-        <v>0.008197557181119919</v>
+        <v>0.007212639320641756</v>
       </c>
       <c r="ED5" t="n">
-        <v>0.008328283205628395</v>
+        <v>0.01088503561913967</v>
       </c>
       <c r="EE5" t="n">
-        <v>0.004742323886603117</v>
+        <v>0.03437525406479836</v>
       </c>
       <c r="EF5" t="n">
-        <v>0.0002509297337383032</v>
+        <v>0.02266064658761024</v>
       </c>
       <c r="EG5" t="n">
-        <v>0.0005618197610601783</v>
+        <v>0.04797231778502464</v>
       </c>
       <c r="EH5" t="n">
-        <v>0.004847126081585884</v>
+        <v>0.01789437048137188</v>
       </c>
       <c r="EI5" t="n">
-        <v>0.003859253134578466</v>
+        <v>0.01973483338952065</v>
       </c>
       <c r="EJ5" t="n">
-        <v>0.003948469646275043</v>
+        <v>0.02730172127485275</v>
       </c>
       <c r="EK5" t="n">
-        <v>0.01494686026126146</v>
+        <v>0.02231922931969166</v>
       </c>
       <c r="EL5" t="n">
-        <v>0.001622650073841214</v>
+        <v>0.01501351594924927</v>
       </c>
       <c r="EM5" t="n">
-        <v>0.006863743532449007</v>
+        <v>0.01658318750560284</v>
       </c>
       <c r="EN5" t="n">
-        <v>0.003727766452357173</v>
+        <v>0.01737763732671738</v>
       </c>
       <c r="EO5" t="n">
-        <v>0.004783010110259056</v>
+        <v>0.0207743588835001</v>
       </c>
       <c r="EP5" t="n">
-        <v>0.001251021167263389</v>
+        <v>0.04598670080304146</v>
       </c>
       <c r="EQ5" t="n">
-        <v>0.006773286499083042</v>
+        <v>0.03212662413716316</v>
       </c>
       <c r="ER5" t="n">
-        <v>0.00196793070062995</v>
+        <v>0.01084612496197224</v>
       </c>
       <c r="ES5" t="n">
-        <v>0.005704887211322784</v>
+        <v>0.03875420987606049</v>
       </c>
       <c r="ET5" t="n">
-        <v>0.0002761082723736763</v>
+        <v>0.06365338712930679</v>
       </c>
       <c r="EU5" t="n">
-        <v>0.004158764146268368</v>
+        <v>0.0007234807126224041</v>
       </c>
       <c r="EV5" t="n">
-        <v>0.03824516758322716</v>
+        <v>0.01428090035915375</v>
       </c>
       <c r="EW5" t="n">
-        <v>0.006763407960534096</v>
+        <v>0.03084702417254448</v>
       </c>
       <c r="EX5" t="n">
-        <v>0.001955523155629635</v>
+        <v>0.008988975547254086</v>
       </c>
       <c r="EY5" t="n">
-        <v>0.004264084622263908</v>
+        <v>0.05112762004137039</v>
       </c>
       <c r="EZ5" t="n">
-        <v>0.00235453643836081</v>
+        <v>0.03310339897871017</v>
       </c>
       <c r="FA5" t="n">
-        <v>0.001128086820244789</v>
+        <v>0.0006201062351465225</v>
       </c>
       <c r="FB5" t="n">
-        <v>0.009139318950474262</v>
+        <v>0.02468726597726345</v>
       </c>
       <c r="FC5" t="n">
-        <v>0.01637377962470055</v>
+        <v>0.05908545479178429</v>
       </c>
       <c r="FD5" t="n">
-        <v>0.002312061609700322</v>
+        <v>0.0184403657913208</v>
       </c>
       <c r="FE5" t="n">
-        <v>0.009864192456007004</v>
+        <v>0.002436814596876502</v>
       </c>
       <c r="FF5" t="n">
-        <v>0.0009561344049870968</v>
+        <v>0.009104698896408081</v>
       </c>
       <c r="FG5" t="n">
-        <v>0.007574503310024738</v>
+        <v>0.005607479251921177</v>
       </c>
       <c r="FH5" t="n">
-        <v>0.001919810078106821</v>
+        <v>0.05403695628046989</v>
       </c>
       <c r="FI5" t="n">
-        <v>0.004731266759335995</v>
+        <v>0.02730271965265274</v>
       </c>
       <c r="FJ5" t="n">
-        <v>0.01625611633062363</v>
+        <v>0.03284872323274612</v>
       </c>
       <c r="FK5" t="n">
-        <v>0.002961842343211174</v>
+        <v>0.03220655024051666</v>
       </c>
       <c r="FL5" t="n">
-        <v>0.01267967559397221</v>
+        <v>0.01924324035644531</v>
       </c>
       <c r="FM5" t="n">
-        <v>0.0003070312086492777</v>
+        <v>0.01897728815674782</v>
       </c>
       <c r="FN5" t="n">
-        <v>0.01782587170600891</v>
+        <v>0.01608742028474808</v>
       </c>
       <c r="FO5" t="n">
-        <v>0.009724275209009647</v>
+        <v>0.05172647163271904</v>
       </c>
       <c r="FP5" t="n">
-        <v>0.02074801363050938</v>
+        <v>0.02953785844147205</v>
       </c>
       <c r="FQ5" t="n">
-        <v>0.007115581538528204</v>
+        <v>0.03316254913806915</v>
       </c>
       <c r="FR5" t="n">
-        <v>0.006071174517273903</v>
+        <v>0.07634983956813812</v>
       </c>
       <c r="FS5" t="n">
-        <v>0.002859264146536589</v>
+        <v>0.07023119926452637</v>
       </c>
       <c r="FT5" t="n">
-        <v>0.01628576964139938</v>
+        <v>0.02612372487783432</v>
       </c>
       <c r="FU5" t="n">
-        <v>0.02153266221284866</v>
+        <v>0.006420166231691837</v>
       </c>
       <c r="FV5" t="n">
-        <v>0.003224274609237909</v>
+        <v>0.008115050382912159</v>
       </c>
       <c r="FW5" t="n">
-        <v>0.01549624279141426</v>
+        <v>0.1092225760221481</v>
       </c>
       <c r="FX5" t="n">
-        <v>0.01640106737613678</v>
+        <v>0.06021880358457565</v>
       </c>
       <c r="FY5" t="n">
-        <v>0.01463032606989145</v>
+        <v>0.0593208447098732</v>
       </c>
       <c r="FZ5" t="n">
-        <v>0.008251173421740532</v>
+        <v>0.04546085372567177</v>
       </c>
       <c r="GA5" t="n">
-        <v>0.01524379570037127</v>
+        <v>0.09658442437648773</v>
       </c>
       <c r="GB5" t="n">
-        <v>0.001966021023690701</v>
+        <v>0.01437768340110779</v>
       </c>
       <c r="GC5" t="n">
-        <v>0.01350612379610538</v>
+        <v>0.02300372160971165</v>
       </c>
       <c r="GD5" t="n">
-        <v>0.002252007368952036</v>
+        <v>0.007053887471556664</v>
       </c>
       <c r="GE5" t="n">
-        <v>0.007737987674772739</v>
+        <v>0.0005919290706515312</v>
       </c>
       <c r="GF5" t="n">
-        <v>0.01858247257769108</v>
+        <v>0.01291926670819521</v>
       </c>
       <c r="GG5" t="n">
-        <v>0.01448941510170698</v>
+        <v>0.00660539697855711</v>
       </c>
     </row>
     <row r="6">
@@ -3844,571 +3844,571 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>0.0007232131902128458</v>
+        <v>0.01385347917675972</v>
       </c>
       <c r="B7" t="n">
-        <v>0.07323697209358215</v>
+        <v>0.820382833480835</v>
       </c>
       <c r="C7" t="n">
-        <v>0.009332195855677128</v>
+        <v>0.07605451345443726</v>
       </c>
       <c r="D7" t="n">
-        <v>0.03504924103617668</v>
+        <v>0.3075952529907227</v>
       </c>
       <c r="E7" t="n">
-        <v>0.03907980024814606</v>
+        <v>0.1295354664325714</v>
       </c>
       <c r="F7" t="n">
-        <v>0.02990692853927612</v>
+        <v>0.4866538643836975</v>
       </c>
       <c r="G7" t="n">
-        <v>0.01423895452171564</v>
+        <v>0.05846915394067764</v>
       </c>
       <c r="H7" t="n">
-        <v>0.02402032166719437</v>
+        <v>0.1066431552171707</v>
       </c>
       <c r="I7" t="n">
-        <v>0.001835681730881333</v>
+        <v>0.1281065791845322</v>
       </c>
       <c r="J7" t="n">
-        <v>0.0008072894997894764</v>
+        <v>0.1855143308639526</v>
       </c>
       <c r="K7" t="n">
-        <v>0.06137196347117424</v>
+        <v>0.9423661231994629</v>
       </c>
       <c r="L7" t="n">
-        <v>0.003436010796576738</v>
+        <v>0.07180631160736084</v>
       </c>
       <c r="M7" t="n">
-        <v>0.02113978937268257</v>
+        <v>0.5605049133300781</v>
       </c>
       <c r="N7" t="n">
-        <v>0.02477126754820347</v>
+        <v>0.1328899562358856</v>
       </c>
       <c r="O7" t="n">
-        <v>0.02941547520458698</v>
+        <v>0.4346943795681</v>
       </c>
       <c r="P7" t="n">
-        <v>0.01300888508558273</v>
+        <v>0.1443999856710434</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.004631909541785717</v>
+        <v>0.1686467975378036</v>
       </c>
       <c r="R7" t="n">
-        <v>0.003752089571207762</v>
+        <v>0.1453820466995239</v>
       </c>
       <c r="S7" t="n">
-        <v>0.001470937277190387</v>
+        <v>0.08127311617136002</v>
       </c>
       <c r="T7" t="n">
-        <v>0.01161795295774937</v>
+        <v>0.2312881052494049</v>
       </c>
       <c r="U7" t="n">
-        <v>0.001025028061121702</v>
+        <v>0.02580677159130573</v>
       </c>
       <c r="V7" t="n">
-        <v>0.01237614452838898</v>
+        <v>0.1404941976070404</v>
       </c>
       <c r="W7" t="n">
-        <v>0.009779474698007107</v>
+        <v>0.03124493174254894</v>
       </c>
       <c r="X7" t="n">
-        <v>0.002558631589636207</v>
+        <v>0.03716154024004936</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.005269096232950687</v>
+        <v>0.04780488833785057</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.01102349441498518</v>
+        <v>0.04639687389135361</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.006451552733778954</v>
+        <v>0.04518020153045654</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.004477008245885372</v>
+        <v>0.0524611622095108</v>
       </c>
       <c r="AC7" t="n">
-        <v>0.00576293095946312</v>
+        <v>0.0516737587749958</v>
       </c>
       <c r="AD7" t="n">
-        <v>0.002322602085769176</v>
+        <v>0.08177242428064346</v>
       </c>
       <c r="AE7" t="n">
-        <v>0.005636401008814573</v>
+        <v>0.1297238767147064</v>
       </c>
       <c r="AF7" t="n">
-        <v>0.006834377534687519</v>
+        <v>0.2162785530090332</v>
       </c>
       <c r="AG7" t="n">
-        <v>0.00496002659201622</v>
+        <v>0.00604952871799469</v>
       </c>
       <c r="AH7" t="n">
-        <v>0.008293246850371361</v>
+        <v>0.07343363761901855</v>
       </c>
       <c r="AI7" t="n">
-        <v>0.008338660933077335</v>
+        <v>0.2761081159114838</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0.003816619981080294</v>
+        <v>0.04913420230150223</v>
       </c>
       <c r="AK7" t="n">
-        <v>0.006512521766126156</v>
+        <v>0.04194799065589905</v>
       </c>
       <c r="AL7" t="n">
-        <v>0.01823567971587181</v>
+        <v>0.2523787319660187</v>
       </c>
       <c r="AM7" t="n">
-        <v>0.002584610600024462</v>
+        <v>0.002784254029393196</v>
       </c>
       <c r="AN7" t="n">
-        <v>0.003697742242366076</v>
+        <v>0.04792205989360809</v>
       </c>
       <c r="AO7" t="n">
-        <v>0.001033389125950634</v>
+        <v>0.1423359215259552</v>
       </c>
       <c r="AP7" t="n">
-        <v>0.01373051293194294</v>
+        <v>0.1717696040868759</v>
       </c>
       <c r="AQ7" t="n">
-        <v>0.0006689894944429398</v>
+        <v>0.09517192095518112</v>
       </c>
       <c r="AR7" t="n">
-        <v>0.009864936582744122</v>
+        <v>0.3009786605834961</v>
       </c>
       <c r="AS7" t="n">
-        <v>0.00747118704020977</v>
+        <v>0.01442037988454103</v>
       </c>
       <c r="AT7" t="n">
-        <v>0.005787738598883152</v>
+        <v>0.07653211057186127</v>
       </c>
       <c r="AU7" t="n">
-        <v>0.05509481579065323</v>
+        <v>0.8325841426849365</v>
       </c>
       <c r="AV7" t="n">
-        <v>0.000830640085041523</v>
+        <v>0.001679226756095886</v>
       </c>
       <c r="AW7" t="n">
-        <v>0.003879271680489182</v>
+        <v>0.1159069463610649</v>
       </c>
       <c r="AX7" t="n">
-        <v>0.01087738573551178</v>
+        <v>0.0103595182299614</v>
       </c>
       <c r="AY7" t="n">
-        <v>0.01630708016455173</v>
+        <v>0.2284907251596451</v>
       </c>
       <c r="AZ7" t="n">
-        <v>0.002000659937039018</v>
+        <v>0.08604785799980164</v>
       </c>
       <c r="BA7" t="n">
-        <v>0.0139271579682827</v>
+        <v>0.018988236784935</v>
       </c>
       <c r="BB7" t="n">
-        <v>0.003385134972631931</v>
+        <v>0.09029976278543472</v>
       </c>
       <c r="BC7" t="n">
-        <v>0.0003292891196906567</v>
+        <v>0.06222575902938843</v>
       </c>
       <c r="BD7" t="n">
-        <v>0.008661854080855846</v>
+        <v>0.1588167101144791</v>
       </c>
       <c r="BE7" t="n">
-        <v>0.007805638946592808</v>
+        <v>0.1260969787836075</v>
       </c>
       <c r="BF7" t="n">
-        <v>0.008548934012651443</v>
+        <v>0.111993245780468</v>
       </c>
       <c r="BG7" t="n">
-        <v>0.02081038057804108</v>
+        <v>0.2474537193775177</v>
       </c>
       <c r="BH7" t="n">
-        <v>0.003732822835445404</v>
+        <v>0.1414233446121216</v>
       </c>
       <c r="BI7" t="n">
-        <v>0.01327074877917767</v>
+        <v>0.04269204288721085</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0.012590067461133</v>
+        <v>0.09635801613330841</v>
       </c>
       <c r="BK7" t="n">
-        <v>0.003749889554455876</v>
+        <v>0.1402001976966858</v>
       </c>
       <c r="BL7" t="n">
-        <v>0.009532762691378593</v>
+        <v>0.1134670227766037</v>
       </c>
       <c r="BM7" t="n">
-        <v>0.0115637443959713</v>
+        <v>0.02299496904015541</v>
       </c>
       <c r="BN7" t="n">
-        <v>0.003474289085716009</v>
+        <v>0.04135503992438316</v>
       </c>
       <c r="BO7" t="n">
-        <v>0.003604021389037371</v>
+        <v>0.06106346845626831</v>
       </c>
       <c r="BP7" t="n">
-        <v>0.002366311615332961</v>
+        <v>0.05425621941685677</v>
       </c>
       <c r="BQ7" t="n">
-        <v>0.006875894498080015</v>
+        <v>0.1031157597899437</v>
       </c>
       <c r="BR7" t="n">
-        <v>0.003566626459360123</v>
+        <v>0.1753068417310715</v>
       </c>
       <c r="BS7" t="n">
-        <v>0.005741163156926632</v>
+        <v>0.09307581931352615</v>
       </c>
       <c r="BT7" t="n">
-        <v>0.007002085447311401</v>
+        <v>0.07226714491844177</v>
       </c>
       <c r="BU7" t="n">
-        <v>0.006812591571360826</v>
+        <v>0.1095993593335152</v>
       </c>
       <c r="BV7" t="n">
-        <v>0.03491942957043648</v>
+        <v>0.6698492169380188</v>
       </c>
       <c r="BW7" t="n">
-        <v>0.01311877556145191</v>
+        <v>0.02788223326206207</v>
       </c>
       <c r="BX7" t="n">
-        <v>0.004204056225717068</v>
+        <v>0.2067789733409882</v>
       </c>
       <c r="BY7" t="n">
-        <v>0.008220972493290901</v>
+        <v>0.07719158381223679</v>
       </c>
       <c r="BZ7" t="n">
-        <v>0.002191991545259953</v>
+        <v>0.1149242669343948</v>
       </c>
       <c r="CA7" t="n">
-        <v>0.003524231957271695</v>
+        <v>0.1008457988500595</v>
       </c>
       <c r="CB7" t="n">
-        <v>0.003626296995207667</v>
+        <v>0.01271705236285925</v>
       </c>
       <c r="CC7" t="n">
-        <v>0.006016177125275135</v>
+        <v>0.0012122867628932</v>
       </c>
       <c r="CD7" t="n">
-        <v>0.002028041053563356</v>
+        <v>0.005141805857419968</v>
       </c>
       <c r="CE7" t="n">
-        <v>0.01014235615730286</v>
+        <v>0.2530069649219513</v>
       </c>
       <c r="CF7" t="n">
-        <v>0.002535735722631216</v>
+        <v>0.01594003476202488</v>
       </c>
       <c r="CG7" t="n">
-        <v>0.005896788090467453</v>
+        <v>0.02394979074597359</v>
       </c>
       <c r="CH7" t="n">
-        <v>0.001846517785452306</v>
+        <v>0.06648662686347961</v>
       </c>
       <c r="CI7" t="n">
-        <v>0.005169836804270744</v>
+        <v>0.09785216301679611</v>
       </c>
       <c r="CJ7" t="n">
-        <v>0.004077254328876734</v>
+        <v>0.01789109781384468</v>
       </c>
       <c r="CK7" t="n">
-        <v>0.004216906614601612</v>
+        <v>0.04804365336894989</v>
       </c>
       <c r="CL7" t="n">
-        <v>0.003804543521255255</v>
+        <v>0.02388945408165455</v>
       </c>
       <c r="CM7" t="n">
-        <v>0.008372101932764053</v>
+        <v>0.1262245625257492</v>
       </c>
       <c r="CN7" t="n">
-        <v>0.005565297789871693</v>
+        <v>0.3504915535449982</v>
       </c>
       <c r="CO7" t="n">
-        <v>0.0001307912170886993</v>
+        <v>0.00244604516774416</v>
       </c>
       <c r="CP7" t="n">
-        <v>0.009431169368326664</v>
+        <v>0.1132896021008492</v>
       </c>
       <c r="CQ7" t="n">
-        <v>0.009866555221378803</v>
+        <v>0.1163364946842194</v>
       </c>
       <c r="CR7" t="n">
-        <v>0.004935581237077713</v>
+        <v>0.003770653158426285</v>
       </c>
       <c r="CS7" t="n">
-        <v>0.01467872504144907</v>
+        <v>0.03611505031585693</v>
       </c>
       <c r="CT7" t="n">
-        <v>0.01483918819576502</v>
+        <v>0.1975916028022766</v>
       </c>
       <c r="CU7" t="n">
-        <v>0.001548848696984351</v>
+        <v>0.02144400775432587</v>
       </c>
       <c r="CV7" t="n">
-        <v>0.00202804640866816</v>
+        <v>0.04871054738759995</v>
       </c>
       <c r="CW7" t="n">
-        <v>0.008618553169071674</v>
+        <v>0.2608991861343384</v>
       </c>
       <c r="CX7" t="n">
-        <v>0.003293181536719203</v>
+        <v>0.005459161475300789</v>
       </c>
       <c r="CY7" t="n">
-        <v>0.008700260892510414</v>
+        <v>0.03466533496975899</v>
       </c>
       <c r="CZ7" t="n">
-        <v>0.001340007525868714</v>
+        <v>0.07819946110248566</v>
       </c>
       <c r="DA7" t="n">
-        <v>0.00907435454428196</v>
+        <v>0.1143166869878769</v>
       </c>
       <c r="DB7" t="n">
-        <v>0.003103140508756042</v>
+        <v>0.01471762079745531</v>
       </c>
       <c r="DC7" t="n">
-        <v>0.005464321933686733</v>
+        <v>0.03142532706260681</v>
       </c>
       <c r="DD7" t="n">
-        <v>0.0009085648925974965</v>
+        <v>0.02222326956689358</v>
       </c>
       <c r="DE7" t="n">
-        <v>0.003284411272034049</v>
+        <v>0.0796862468123436</v>
       </c>
       <c r="DF7" t="n">
-        <v>0.008281569927930832</v>
+        <v>0.328600287437439</v>
       </c>
       <c r="DG7" t="n">
-        <v>0.003406904870644212</v>
+        <v>0.2250547707080841</v>
       </c>
       <c r="DH7" t="n">
-        <v>0.02576043829321861</v>
+        <v>0.00401512673124671</v>
       </c>
       <c r="DI7" t="n">
-        <v>0.01100722700357437</v>
+        <v>0.2284659147262573</v>
       </c>
       <c r="DJ7" t="n">
-        <v>0.003726084250956774</v>
+        <v>0.2772091031074524</v>
       </c>
       <c r="DK7" t="n">
-        <v>0.01260572671890259</v>
+        <v>0.05773026496171951</v>
       </c>
       <c r="DL7" t="n">
-        <v>0.006388726644217968</v>
+        <v>0.0812721848487854</v>
       </c>
       <c r="DM7" t="n">
-        <v>0.007457803469151258</v>
+        <v>0.1580039709806442</v>
       </c>
       <c r="DN7" t="n">
-        <v>0.00201886729337275</v>
+        <v>0.01921744644641876</v>
       </c>
       <c r="DO7" t="n">
-        <v>0.006989662069827318</v>
+        <v>0.1684867143630981</v>
       </c>
       <c r="DP7" t="n">
-        <v>0.00460658548399806</v>
+        <v>0.02651140280067921</v>
       </c>
       <c r="DQ7" t="n">
-        <v>0.005305519327521324</v>
+        <v>0.1193765103816986</v>
       </c>
       <c r="DR7" t="n">
-        <v>0.0007051688153296709</v>
+        <v>0.06467391550540924</v>
       </c>
       <c r="DS7" t="n">
-        <v>0.008943047374486923</v>
+        <v>0.07944650202989578</v>
       </c>
       <c r="DT7" t="n">
-        <v>0.00282702874392271</v>
+        <v>0.0002145115286111832</v>
       </c>
       <c r="DU7" t="n">
-        <v>0.003905817167833447</v>
+        <v>0.03879018872976303</v>
       </c>
       <c r="DV7" t="n">
-        <v>0.003172978525981307</v>
+        <v>0.009191062301397324</v>
       </c>
       <c r="DW7" t="n">
-        <v>0.003830681322142482</v>
+        <v>0.1041234135627747</v>
       </c>
       <c r="DX7" t="n">
-        <v>0.002291380893439054</v>
+        <v>0.09566551446914673</v>
       </c>
       <c r="DY7" t="n">
-        <v>0.008718498051166534</v>
+        <v>0.01231788098812103</v>
       </c>
       <c r="DZ7" t="n">
-        <v>9.98261384665966e-05</v>
+        <v>0.03352492675185204</v>
       </c>
       <c r="EA7" t="n">
-        <v>0.005418511107563972</v>
+        <v>0.03727772831916809</v>
       </c>
       <c r="EB7" t="n">
-        <v>0.006144034210592508</v>
+        <v>0.09114846587181091</v>
       </c>
       <c r="EC7" t="n">
-        <v>0.0003257442731410265</v>
+        <v>0.02355768159031868</v>
       </c>
       <c r="ED7" t="n">
-        <v>0.005076531320810318</v>
+        <v>0.06221185252070427</v>
       </c>
       <c r="EE7" t="n">
-        <v>0.0001260429853573442</v>
+        <v>0.2288725078105927</v>
       </c>
       <c r="EF7" t="n">
-        <v>0.002025339286774397</v>
+        <v>0.05903680995106697</v>
       </c>
       <c r="EG7" t="n">
-        <v>0.00987965427339077</v>
+        <v>0.08992747962474823</v>
       </c>
       <c r="EH7" t="n">
-        <v>0.00417507765814662</v>
+        <v>0.04015081003308296</v>
       </c>
       <c r="EI7" t="n">
-        <v>0.003055643057450652</v>
+        <v>0.1234199330210686</v>
       </c>
       <c r="EJ7" t="n">
-        <v>0.01095179095864296</v>
+        <v>0.1418476104736328</v>
       </c>
       <c r="EK7" t="n">
-        <v>0.004819945897907019</v>
+        <v>0.01587668061256409</v>
       </c>
       <c r="EL7" t="n">
-        <v>0.004992373287677765</v>
+        <v>0.0311281681060791</v>
       </c>
       <c r="EM7" t="n">
-        <v>0.002924009459093213</v>
+        <v>0.05412626639008522</v>
       </c>
       <c r="EN7" t="n">
-        <v>0.0001331319799646735</v>
+        <v>0.009556474164128304</v>
       </c>
       <c r="EO7" t="n">
-        <v>0.0003072270192205906</v>
+        <v>0.08976231515407562</v>
       </c>
       <c r="EP7" t="n">
-        <v>0.002828328870236874</v>
+        <v>0.161364808678627</v>
       </c>
       <c r="EQ7" t="n">
-        <v>0.009562257677316666</v>
+        <v>0.02759883180260658</v>
       </c>
       <c r="ER7" t="n">
-        <v>0.008943933062255383</v>
+        <v>0.01304362714290619</v>
       </c>
       <c r="ES7" t="n">
-        <v>0.005487105809152126</v>
+        <v>0.1748634874820709</v>
       </c>
       <c r="ET7" t="n">
-        <v>0.01350124645978212</v>
+        <v>0.02110873721539974</v>
       </c>
       <c r="EU7" t="n">
-        <v>0.004083711188286543</v>
+        <v>0.02220677770674229</v>
       </c>
       <c r="EV7" t="n">
-        <v>0.01268477737903595</v>
+        <v>0.02123962715268135</v>
       </c>
       <c r="EW7" t="n">
-        <v>0.00130204507149756</v>
+        <v>0.01231794152408838</v>
       </c>
       <c r="EX7" t="n">
-        <v>0.001483271713368595</v>
+        <v>0.00461505725979805</v>
       </c>
       <c r="EY7" t="n">
-        <v>0.007739189546555281</v>
+        <v>0.2786702513694763</v>
       </c>
       <c r="EZ7" t="n">
-        <v>0.002272582147270441</v>
+        <v>0.02884087339043617</v>
       </c>
       <c r="FA7" t="n">
-        <v>0.007827014662325382</v>
+        <v>0.02824859879910946</v>
       </c>
       <c r="FB7" t="n">
-        <v>1.636327942833304e-05</v>
+        <v>0.08997447788715363</v>
       </c>
       <c r="FC7" t="n">
-        <v>0.006114540621638298</v>
+        <v>0.09267577528953552</v>
       </c>
       <c r="FD7" t="n">
-        <v>0.005261032842099667</v>
+        <v>0.02319201827049255</v>
       </c>
       <c r="FE7" t="n">
-        <v>0.005188500508666039</v>
+        <v>0.02043864689767361</v>
       </c>
       <c r="FF7" t="n">
-        <v>0.003815019503235817</v>
+        <v>0.04338761419057846</v>
       </c>
       <c r="FG7" t="n">
-        <v>0.002184635959565639</v>
+        <v>0.04711943119764328</v>
       </c>
       <c r="FH7" t="n">
-        <v>0.006319383159279823</v>
+        <v>0.1600345373153687</v>
       </c>
       <c r="FI7" t="n">
-        <v>0.009481464512646198</v>
+        <v>0.02607860416173935</v>
       </c>
       <c r="FJ7" t="n">
-        <v>0.01087071746587753</v>
+        <v>0.02144878357648849</v>
       </c>
       <c r="FK7" t="n">
-        <v>0.002307700924575329</v>
+        <v>0.09582120180130005</v>
       </c>
       <c r="FL7" t="n">
-        <v>0.0003116352017968893</v>
+        <v>0.1336044371128082</v>
       </c>
       <c r="FM7" t="n">
-        <v>1.612585037946701e-05</v>
+        <v>0.0622415766119957</v>
       </c>
       <c r="FN7" t="n">
-        <v>0.003442005719989538</v>
+        <v>0.1074658706784248</v>
       </c>
       <c r="FO7" t="n">
-        <v>0.005069048143923283</v>
+        <v>0.1327780038118362</v>
       </c>
       <c r="FP7" t="n">
-        <v>0.0002755799796432257</v>
+        <v>0.0705939307808876</v>
       </c>
       <c r="FQ7" t="n">
-        <v>0.01091440580785275</v>
+        <v>0.2197619378566742</v>
       </c>
       <c r="FR7" t="n">
-        <v>0.01026723347604275</v>
+        <v>9.468942880630493e-05</v>
       </c>
       <c r="FS7" t="n">
-        <v>0.01144157256931067</v>
+        <v>0.2309572696685791</v>
       </c>
       <c r="FT7" t="n">
-        <v>0.007495467085391283</v>
+        <v>0.0982951819896698</v>
       </c>
       <c r="FU7" t="n">
-        <v>0.0003429681528359652</v>
+        <v>0.05211995542049408</v>
       </c>
       <c r="FV7" t="n">
-        <v>0.008480323478579521</v>
+        <v>0.1687512248754501</v>
       </c>
       <c r="FW7" t="n">
-        <v>0.004465073347091675</v>
+        <v>0.08162209391593933</v>
       </c>
       <c r="FX7" t="n">
-        <v>0.0004247609758749604</v>
+        <v>0.04105102270841599</v>
       </c>
       <c r="FY7" t="n">
-        <v>0.01021525263786316</v>
+        <v>0.1124769225716591</v>
       </c>
       <c r="FZ7" t="n">
-        <v>0.001777382218278944</v>
+        <v>0.156213715672493</v>
       </c>
       <c r="GA7" t="n">
-        <v>0.00111219403333962</v>
+        <v>0.009439803659915924</v>
       </c>
       <c r="GB7" t="n">
-        <v>0.006465183105319738</v>
+        <v>0.05046334117650986</v>
       </c>
       <c r="GC7" t="n">
-        <v>0.007010583765804768</v>
+        <v>0.06591905653476715</v>
       </c>
       <c r="GD7" t="n">
-        <v>0.008239729329943657</v>
+        <v>0.02340422570705414</v>
       </c>
       <c r="GE7" t="n">
-        <v>0.0301455594599247</v>
+        <v>0.08386961370706558</v>
       </c>
       <c r="GF7" t="n">
-        <v>0.002685714513063431</v>
+        <v>0.02634806558489799</v>
       </c>
       <c r="GG7" t="n">
-        <v>0.0004237866960465908</v>
+        <v>0.04713568091392517</v>
       </c>
     </row>
     <row r="8">
